--- a/Jal Rekha CMMIL5 Artefacts/new Cycle 4 Jan26 May26/CR/Jal_Rekha_CR_Log_Cycle4_Jan_May_2026_V1_5.xlsx
+++ b/Jal Rekha CMMIL5 Artefacts/new Cycle 4 Jan26 May26/CR/Jal_Rekha_CR_Log_Cycle4_Jan_May_2026_V1_5.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190" firstSheet="8" activeTab="13"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190" firstSheet="8" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="Version" sheetId="1" r:id="rId1"/>
